--- a/timesheets/Moritz.xlsx
+++ b/timesheets/Moritz.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\morit\Documents\A_Uni\Notes\DS5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7F8508-7E2F-4DE7-9D03-942669E395EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C71B4D3-47B0-4C6F-966A-11C1ADA395C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39160" yWindow="760" windowWidth="28800" windowHeight="15910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="71">
   <si>
     <t>Date</t>
   </si>
@@ -51,6 +51,204 @@
   </si>
   <si>
     <t>Sum Hours</t>
+  </si>
+  <si>
+    <t>10.03.</t>
+  </si>
+  <si>
+    <t>Preperation for first meeting with data coaches</t>
+  </si>
+  <si>
+    <t>13.03.</t>
+  </si>
+  <si>
+    <t>Meeting with data coaches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.03. </t>
+  </si>
+  <si>
+    <t>Initial project proposal: project description</t>
+  </si>
+  <si>
+    <t>23.03.</t>
+  </si>
+  <si>
+    <t>Meeting with WU supervisor about Feedback and team intern discussion</t>
+  </si>
+  <si>
+    <t>19.03.</t>
+  </si>
+  <si>
+    <t>Team meeting</t>
+  </si>
+  <si>
+    <t>26.03.</t>
+  </si>
+  <si>
+    <t>24.03.</t>
+  </si>
+  <si>
+    <t>Refined project plan: project description</t>
+  </si>
+  <si>
+    <t>01.04.</t>
+  </si>
+  <si>
+    <t>Designing data pipeline</t>
+  </si>
+  <si>
+    <t>09.04.</t>
+  </si>
+  <si>
+    <t>09.03.</t>
+  </si>
+  <si>
+    <t>12.04.</t>
+  </si>
+  <si>
+    <t>Constructing data pipeline</t>
+  </si>
+  <si>
+    <t>Creating first model</t>
+  </si>
+  <si>
+    <t>13.04.</t>
+  </si>
+  <si>
+    <t>Refining first model</t>
+  </si>
+  <si>
+    <t>14.04.</t>
+  </si>
+  <si>
+    <t>Training first model</t>
+  </si>
+  <si>
+    <t>16.04.</t>
+  </si>
+  <si>
+    <t>Testing first model</t>
+  </si>
+  <si>
+    <t>17.04.</t>
+  </si>
+  <si>
+    <t>Creating Intermediate Report and slides</t>
+  </si>
+  <si>
+    <t>22.04.</t>
+  </si>
+  <si>
+    <t>Intermediate Presentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03.05. </t>
+  </si>
+  <si>
+    <t>Sparring group</t>
+  </si>
+  <si>
+    <t>05.05.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Updating first model </t>
+  </si>
+  <si>
+    <t>07.05.</t>
+  </si>
+  <si>
+    <t>14.05.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Improving model </t>
+  </si>
+  <si>
+    <t>Improving ground truth</t>
+  </si>
+  <si>
+    <t>16.05.</t>
+  </si>
+  <si>
+    <t>21.05.</t>
+  </si>
+  <si>
+    <t>28.05.</t>
+  </si>
+  <si>
+    <t>Modifying loss and usable pixel selection for model</t>
+  </si>
+  <si>
+    <t>18.05.</t>
+  </si>
+  <si>
+    <t>22.05.</t>
+  </si>
+  <si>
+    <t>Commenting code</t>
+  </si>
+  <si>
+    <t>29.05.</t>
+  </si>
+  <si>
+    <t>Writing final draft Methodology</t>
+  </si>
+  <si>
+    <t>30.05.</t>
+  </si>
+  <si>
+    <t>Writing final draft Implementation and Results</t>
+  </si>
+  <si>
+    <t>31.05.</t>
+  </si>
+  <si>
+    <t>Preparing slides for final presentation</t>
+  </si>
+  <si>
+    <t>24.05.</t>
+  </si>
+  <si>
+    <t>Getting predictions and visualizations</t>
+  </si>
+  <si>
+    <t>Training and refining final model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09.06. </t>
+  </si>
+  <si>
+    <t>10.06.</t>
+  </si>
+  <si>
+    <t>Sparring minutes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.06. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refining final report </t>
+  </si>
+  <si>
+    <t>Presentation slides improvements and graphics</t>
+  </si>
+  <si>
+    <t>Preparing text for final presentation</t>
+  </si>
+  <si>
+    <t>14.06.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.06. </t>
+  </si>
+  <si>
+    <t>Final presentation</t>
+  </si>
+  <si>
+    <t>27.06.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finalizing final report </t>
   </si>
 </sst>
 </file>
@@ -369,12 +567,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" customWidth="1"/>
     <col min="2" max="2" width="59.26953125" customWidth="1"/>
-    <col min="8" max="8" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -392,8 +590,8 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
-        <v>46090</v>
+      <c r="A2" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -403,6 +601,424 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>59</v>
+      </c>
+      <c r="B35" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>66</v>
+      </c>
+      <c r="B38" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>67</v>
+      </c>
+      <c r="B39" t="s">
+        <v>68</v>
+      </c>
+      <c r="C39">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40">
         <v>4</v>
       </c>
     </row>
